--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484371_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484371_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3365</v>
+        <v>3.4153</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8882</v>
+        <v>2.967</v>
       </c>
       <c r="F2" t="n">
         <v>0.4482</v>
@@ -610,10 +610,10 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2782</v>
+        <v>0.357</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9606</v>
+        <v>1.0394</v>
       </c>
       <c r="U2" t="n">
         <v>-0.6824</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.731</v>
+        <v>2.0636</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3301</v>
+        <v>-0.5617</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0611</v>
+        <v>2.6253</v>
       </c>
       <c r="G3" t="n">
         <v>3.4386</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4412</v>
+        <v>0.7738</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3272</v>
+        <v>0.4411</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7684</v>
+        <v>0.3327</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6409</v>
+        <v>1.2129</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7755</v>
+        <v>-1.8766</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4163</v>
+        <v>3.0895</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2834</v>
@@ -766,13 +766,13 @@
         <v>0.3907</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3503</v>
+        <v>0.9223</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3247</v>
+        <v>0.2236</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0255</v>
+        <v>0.6987</v>
       </c>
       <c r="V4" t="n">
         <v>1.5507</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1302</v>
+        <v>1.1029</v>
       </c>
       <c r="E5" t="n">
         <v>0.6506</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4796</v>
+        <v>0.4523</v>
       </c>
       <c r="G5" t="n">
         <v>1.8224</v>
@@ -844,13 +844,13 @@
         <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4969</v>
+        <v>-0.5241</v>
       </c>
       <c r="T5" t="n">
         <v>-0.5447</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0478</v>
+        <v>0.0206</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.0132</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7572</v>
+        <v>1.9483</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.044</v>
+        <v>-1.935</v>
       </c>
       <c r="G6" t="n">
         <v>0.4972</v>
@@ -922,13 +922,13 @@
         <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0439</v>
+        <v>0.3439</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1061</v>
+        <v>0.2972</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0622</v>
+        <v>0.0467</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2186</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.019</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3961</v>
+        <v>-1.5627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6859</v>
+        <v>1.5437</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5233</v>
+        <v>0.444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3804</v>
+        <v>0.1203</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0.3237</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9176</v>
+        <v>-0.2105</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3901</v>
+        <v>0.4093</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3077</v>
+        <v>-0.6198</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3944</v>
+        <v>0.6545</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0097</v>
+        <v>-0.2891</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4041</v>
+        <v>0.9435</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.1857</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.201</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>0.7814</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.9135</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.4237</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.4898</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.0549</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.0549</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7891</v>
+        <v>-0.1696</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1694</v>
+        <v>-0.9917</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3803</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.444</v>
+        <v>-0.5233</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1203</v>
+        <v>0.3804</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3237</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2105</v>
+        <v>-0.9176</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4093</v>
+        <v>0.3901</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6198</v>
+        <v>-1.3077</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6545</v>
+        <v>0.3944</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2891</v>
+        <v>-0.0097</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9435</v>
+        <v>0.4041</v>
       </c>
       <c r="P8" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.3674</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9558</v>
+        <v>-0.3728</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5915</v>
+        <v>-0.0192</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3644</v>
+        <v>-0.3536</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="W8" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3431</v>
+        <v>-1.1861</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0044</v>
+        <v>-3.1902</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3475</v>
+        <v>2.0041</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9675</v>
+        <v>-1.0095</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1862</v>
+        <v>-4.1651</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1538</v>
+        <v>3.1555</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9691</v>
+        <v>-0.9003</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0844</v>
+        <v>-2.9778</v>
       </c>
       <c r="L9" t="n">
-        <v>3.8847</v>
+        <v>2.0776</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0016</v>
+        <v>-0.1093</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2707</v>
+        <v>-1.1872</v>
       </c>
       <c r="O9" t="n">
-        <v>0.269</v>
+        <v>1.078</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1255</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.2743</v>
+        <v>-2.3441</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5339</v>
+        <v>0.8783</v>
       </c>
       <c r="T9" t="n">
-        <v>1.142</v>
+        <v>0.4411</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6082</v>
+        <v>0.4372</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.719</v>
+        <v>-0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1675</v>
+        <v>-0.3869</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6215</v>
+        <v>-1.4147</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.898</v>
+        <v>-0.3395</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2765</v>
+        <v>-1.0752</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0095</v>
+        <v>1.9675</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.1651</v>
+        <v>-2.1862</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1555</v>
+        <v>4.1538</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9003</v>
+        <v>3.9691</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9778</v>
+        <v>0.0844</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0776</v>
+        <v>3.8847</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1093</v>
+        <v>-2.0016</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1872</v>
+        <v>-2.2707</v>
       </c>
       <c r="O10" t="n">
-        <v>1.078</v>
+        <v>0.269</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3441</v>
+        <v>-5.2743</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4429</v>
+        <v>0.4623</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2667</v>
+        <v>0.7981</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7096</v>
+        <v>-0.3358</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6642</v>
+        <v>-0.719</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3869</v>
+        <v>0.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3126</v>
+        <v>-2.7853</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7393</v>
+        <v>-4.3754</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4266</v>
+        <v>1.59</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6658</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3147</v>
+        <v>0.2126</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4229</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4721</v>
+        <v>0.6355</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9414</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5422</v>
+        <v>-3.0422</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8884</v>
+        <v>-2.5246</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6538</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8324</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7098</v>
+        <v>-0.2097</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5915</v>
+        <v>-0.2276</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1183</v>
+        <v>0.0178</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6294</v>
+        <v>-3.285</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3254</v>
+        <v>-3.0626</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3041</v>
+        <v>-0.2223</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0139</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4435</v>
+        <v>-0.099</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6657</v>
+        <v>-0.403</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2223</v>
+        <v>0.304</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.3963</v>
+        <v>-4.094</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.2218</v>
+        <v>-12.9191</v>
       </c>
       <c r="F14" t="n">
         <v>8.825100000000001</v>
@@ -1519,16 +1519,16 @@
         <v>12.1376</v>
       </c>
       <c r="J14" t="n">
-        <v>4.896500000000001</v>
+        <v>4.8965</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5040000000000004</v>
+        <v>-0.504</v>
       </c>
       <c r="L14" t="n">
         <v>5.400799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.641399999999999</v>
+        <v>-3.6414</v>
       </c>
       <c r="N14" t="n">
         <v>-10.3786</v>
@@ -1546,13 +1546,13 @@
         <v>14.6508</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2562</v>
+        <v>2.5589</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3356</v>
+        <v>1.638300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9204000000000001</v>
+        <v>0.9203999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-2.0474</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.0351</v>
+        <v>7.5895</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2575</v>
+        <v>2.8419</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7776</v>
+        <v>4.7476</v>
       </c>
       <c r="G15" t="n">
         <v>7.1522</v>
@@ -1624,13 +1624,13 @@
         <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0233</v>
+        <v>0.5778</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5602</v>
+        <v>0.1446</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4631</v>
+        <v>0.4332</v>
       </c>
       <c r="V15" t="n">
         <v>0.0549</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3709</v>
+        <v>4.3811</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2987</v>
+        <v>0.5009</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0722</v>
+        <v>3.8802</v>
       </c>
       <c r="G16" t="n">
         <v>5.7514</v>
@@ -1702,13 +1702,13 @@
         <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.24</v>
+        <v>-0.2298</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2572</v>
+        <v>-1.055</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0172</v>
+        <v>0.8252</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5545</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.077</v>
+        <v>1.8734</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1925</v>
+        <v>-2.3947</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2695</v>
+        <v>4.2682</v>
       </c>
       <c r="G17" t="n">
         <v>-0.426</v>
@@ -1780,13 +1780,13 @@
         <v>2.7348</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4677</v>
+        <v>0.2641</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.341</v>
+        <v>-0.5432</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8087</v>
+        <v>0.8074</v>
       </c>
       <c r="V17" t="n">
         <v>0.2772</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.903</v>
+        <v>1.8611</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.8619</v>
+        <v>-3.2552</v>
       </c>
       <c r="F18" t="n">
-        <v>4.7649</v>
+        <v>5.1163</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7042</v>
@@ -1858,13 +1858,13 @@
         <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2057</v>
+        <v>-0.2476</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3177</v>
+        <v>-0.711</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1121</v>
+        <v>0.4634</v>
       </c>
       <c r="V18" t="n">
         <v>0.6642</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.254</v>
+        <v>0.1038</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3052</v>
+        <v>1.6085</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5592</v>
+        <v>-1.5048</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7181</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5359</v>
+        <v>-0.1781</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3026</v>
+        <v>0.0007</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V19" t="n">
         <v>1.2186</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4371</v>
+        <v>-0.6005</v>
       </c>
       <c r="E20" t="n">
         <v>1.3599</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7971</v>
+        <v>-1.9605</v>
       </c>
       <c r="G20" t="n">
         <v>-1.838</v>
@@ -2014,13 +2014,13 @@
         <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0484</v>
+        <v>-0.2118</v>
       </c>
       <c r="T20" t="n">
         <v>0.2642</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3126</v>
+        <v>-0.476</v>
       </c>
       <c r="V20" t="n">
         <v>0.2772</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. CAAMAÑO ALSINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.93</v>
+        <v>-1.1861</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4307</v>
+        <v>-1.3676</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3607</v>
+        <v>0.1815</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3182</v>
+        <v>-1.5326</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2351</v>
+        <v>-0.8583</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5533</v>
+        <v>-0.6743</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7344</v>
+        <v>-1.3277</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0731</v>
+        <v>-0.6536</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6613</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0526</v>
+        <v>-0.2049</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.838</v>
+        <v>-0.2047</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2146</v>
+        <v>-0.0002</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0291</v>
+        <v>0.0963</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6813</v>
+        <v>-0.0399</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6522</v>
+        <v>0.1362</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6642</v>
+        <v>0.0549</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CAAMAÑO ALSINA</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.47</v>
+        <v>-1.7797</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5698</v>
+        <v>-3.201</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0998</v>
+        <v>1.4212</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5326</v>
+        <v>-2.6759</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8583</v>
+        <v>-2.1236</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6743</v>
+        <v>-0.5523</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3277</v>
+        <v>-2.516</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6536</v>
+        <v>-2.3689</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6741</v>
+        <v>-0.1471</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2049</v>
+        <v>-0.1599</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2047</v>
+        <v>0.2454</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0002</v>
+        <v>-0.4052</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1876</v>
+        <v>-0.194</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2421</v>
+        <v>0.2918</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0545</v>
+        <v>-0.4858</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8841</v>
+        <v>-1.7829</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7899</v>
+        <v>-0.1431</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9059</v>
+        <v>-1.6398</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0643</v>
+        <v>-2.8813</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2167</v>
+        <v>-1.2497</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8476</v>
+        <v>-1.6317</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9192</v>
+        <v>-0.1548</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.142</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3077</v>
+        <v>-0.0128</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1451</v>
+        <v>-2.7265</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3948</v>
+        <v>-1.1077</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5399</v>
+        <v>-1.6188</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6207</v>
+        <v>-0.2923</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.3791</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7033</v>
+        <v>-0.6714</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3869</v>
+        <v>0.6093</v>
       </c>
       <c r="W23" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.3869</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9912</v>
+        <v>-1.8724</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0531</v>
+        <v>-0.7827</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9381</v>
+        <v>-1.0897</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8813</v>
+        <v>-0.3182</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2497</v>
+        <v>0.2351</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6317</v>
+        <v>-0.5533</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1548</v>
+        <v>1.7344</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.142</v>
+        <v>1.0731</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0128</v>
+        <v>0.6613</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7265</v>
+        <v>-2.0526</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1077</v>
+        <v>-0.838</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6188</v>
+        <v>-1.2146</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5005</v>
+        <v>0.0867</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5309</v>
+        <v>0.4679</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9696</v>
+        <v>-0.3812</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6093</v>
+        <v>-0.0549</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.023</v>
+        <v>-2.8425</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0099</v>
+        <v>-3.9922</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9868</v>
+        <v>1.1497</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6759</v>
+        <v>-2.0643</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.1236</v>
+        <v>-0.2167</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5523</v>
+        <v>-1.8476</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.516</v>
+        <v>-1.9192</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.3689</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1471</v>
+        <v>-1.3077</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1599</v>
+        <v>-0.1451</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2454</v>
+        <v>0.3948</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4052</v>
+        <v>-0.5399</v>
       </c>
       <c r="P25" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.3674</v>
       </c>
-      <c r="Q25" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.3441</v>
-      </c>
       <c r="S25" t="n">
-        <v>-1.4373</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5172</v>
+        <v>-0.1196</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9202</v>
+        <v>-0.4596</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2772</v>
+        <v>0.3869</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.2772</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.396599999999998</v>
+        <v>5.744800000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.825099999999999</v>
+        <v>-8.8253</v>
       </c>
       <c r="F26" t="n">
-        <v>13.2216</v>
+        <v>14.5699</v>
       </c>
       <c r="G26" t="n">
         <v>-1.254999999999999</v>
@@ -2455,13 +2455,13 @@
         <v>-12.1377</v>
       </c>
       <c r="J26" t="n">
-        <v>3.641500000000001</v>
+        <v>3.641500000000002</v>
       </c>
       <c r="K26" t="n">
         <v>10.3787</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.736900000000002</v>
+        <v>-6.7369</v>
       </c>
       <c r="M26" t="n">
         <v>-4.896500000000001</v>
@@ -2473,7 +2473,7 @@
         <v>-5.400700000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>5.860500000000001</v>
+        <v>5.860499999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.6505</v>
@@ -2482,13 +2482,13 @@
         <v>20.511</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.256</v>
+        <v>-0.9077999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9204000000000001</v>
+        <v>-0.9204000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3356</v>
+        <v>0.01249999999999973</v>
       </c>
       <c r="V26" t="n">
         <v>2.0473</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484371_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484371_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +653,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0636</v>
+        <v>1.4566</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5617</v>
+        <v>-1.1687</v>
       </c>
       <c r="F3" t="n">
         <v>2.6253</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4386</v>
+        <v>2.8316</v>
       </c>
       <c r="H3" t="n">
         <v>-0.218</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6565</v>
+        <v>3.0495</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2128</v>
+        <v>2.6058</v>
       </c>
       <c r="K3" t="n">
         <v>1.5784</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6344</v>
+        <v>1.0274</v>
       </c>
       <c r="M3" t="n">
         <v>0.2257</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.9962</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0132</v>
+        <v>0.914</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9483</v>
+        <v>0.914</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.935</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4972</v>
+        <v>0.914</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6188</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1216</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6511</v>
+        <v>0.914</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6879</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1538</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3443</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8095</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3439</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2972</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0467</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.019</v>
+        <v>0.607</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5627</v>
+        <v>0.607</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5437</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.444</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1203</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3237</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2105</v>
+        <v>0.607</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4093</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6198</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6545</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2891</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1857</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0152</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.201</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1696</v>
+        <v>0.0132</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9917</v>
+        <v>1.9483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8221000000000001</v>
+        <v>-1.935</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5233</v>
+        <v>0.4972</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3804</v>
+        <v>0.6188</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.1216</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9176</v>
+        <v>1.6511</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3901</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3077</v>
+        <v>0.6879</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3944</v>
+        <v>-1.1538</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0097</v>
+        <v>-0.3443</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4041</v>
+        <v>-0.8095</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3728</v>
+        <v>0.3439</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0192</v>
+        <v>0.2972</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3536</v>
+        <v>0.0467</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0549</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1861</v>
+        <v>-0.1696</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1902</v>
+        <v>-0.9917</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0041</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0095</v>
+        <v>-0.5233</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.1651</v>
+        <v>0.3804</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1555</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9003</v>
+        <v>-0.9176</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.9778</v>
+        <v>0.3901</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0776</v>
+        <v>-1.3077</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1093</v>
+        <v>0.3944</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1872</v>
+        <v>-0.0097</v>
       </c>
       <c r="O9" t="n">
-        <v>1.078</v>
+        <v>0.4041</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8783</v>
+        <v>-0.3728</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4411</v>
+        <v>-0.0192</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4372</v>
+        <v>-0.3536</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6642</v>
+        <v>-0.0549</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3869</v>
+        <v>-0.0549</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4147</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3395</v>
+        <v>-2.4766</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0752</v>
+        <v>1.5437</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9675</v>
+        <v>-0.47</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1862</v>
+        <v>-0.1867</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1538</v>
+        <v>-0.2833</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9691</v>
+        <v>-1.1245</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0844</v>
+        <v>0.1023</v>
       </c>
       <c r="L10" t="n">
-        <v>3.8847</v>
+        <v>-1.2268</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0016</v>
+        <v>0.6545</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2707</v>
+        <v>-0.2891</v>
       </c>
       <c r="O10" t="n">
-        <v>0.269</v>
+        <v>0.9435</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.2743</v>
+        <v>-1.3674</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4623</v>
+        <v>-0.1857</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7981</v>
+        <v>0.0152</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3358</v>
+        <v>-0.201</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.719</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8865</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7853</v>
+        <v>-1.1861</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3754</v>
+        <v>-3.1902</v>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>2.0041</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6658</v>
+        <v>-1.0095</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1512</v>
+        <v>-4.1651</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4854</v>
+        <v>3.1555</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9209</v>
+        <v>-0.9003</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3277</v>
+        <v>-2.9778</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>2.0776</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2551</v>
+        <v>-0.1093</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8235</v>
+        <v>-1.1872</v>
       </c>
       <c r="O11" t="n">
-        <v>1.0786</v>
+        <v>1.078</v>
       </c>
       <c r="P11" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3674</v>
+        <v>-2.3441</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2126</v>
+        <v>0.8783</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4229</v>
+        <v>0.4411</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6355</v>
+        <v>0.4372</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9414</v>
+        <v>-0.6642</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>-0.3869</v>
       </c>
       <c r="X11" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0422</v>
+        <v>-1.4147</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5246</v>
+        <v>-0.3395</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-1.0752</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8324</v>
+        <v>1.9675</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5109</v>
+        <v>-2.1862</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3216</v>
+        <v>4.1538</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1249</v>
+        <v>3.9691</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0614</v>
+        <v>0.0844</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1863</v>
+        <v>3.8847</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7075</v>
+        <v>-2.0016</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5723</v>
+        <v>-2.2707</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1352</v>
+        <v>0.269</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1721</v>
+        <v>-5.2743</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2097</v>
+        <v>0.4623</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2276</v>
+        <v>0.7981</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0178</v>
+        <v>-0.3358</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1675</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.285</v>
+        <v>-2.7853</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0626</v>
+        <v>-4.3754</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2223</v>
+        <v>1.59</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0139</v>
+        <v>-1.6658</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6493</v>
+        <v>-2.1512</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3646</v>
+        <v>0.4854</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5108</v>
+        <v>-1.9209</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5513</v>
+        <v>-1.3277</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0405</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.503</v>
+        <v>0.2551</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.098</v>
+        <v>-0.8235</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4051</v>
+        <v>1.0786</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1488</v>
+        <v>-1.3674</v>
       </c>
       <c r="R13" t="n">
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.099</v>
+        <v>0.2126</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.403</v>
+        <v>-0.4229</v>
       </c>
       <c r="U13" t="n">
-        <v>0.304</v>
+        <v>0.6355</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,1004 +1566,1393 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.094</v>
+        <v>-3.0422</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.9191</v>
+        <v>-2.5246</v>
       </c>
       <c r="F14" t="n">
-        <v>8.825100000000001</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2551</v>
+        <v>-2.8324</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.8827</v>
+        <v>-1.5109</v>
       </c>
       <c r="I14" t="n">
-        <v>12.1376</v>
+        <v>-1.3216</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8965</v>
+        <v>-1.1249</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.504</v>
+        <v>0.0614</v>
       </c>
       <c r="L14" t="n">
-        <v>5.400799999999999</v>
+        <v>-1.1863</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.6414</v>
+        <v>-1.7075</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.3786</v>
+        <v>-1.5723</v>
       </c>
       <c r="O14" t="n">
-        <v>6.737</v>
+        <v>-0.1352</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.860300000000001</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.5111</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>14.6508</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5589</v>
+        <v>-0.2097</v>
       </c>
       <c r="T14" t="n">
-        <v>1.638300000000001</v>
+        <v>-0.2276</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9203999999999999</v>
+        <v>0.0178</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.0474</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1042</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5895</v>
+        <v>-3.285</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8419</v>
+        <v>-3.0626</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7476</v>
+        <v>-0.2223</v>
       </c>
       <c r="G15" t="n">
-        <v>7.1522</v>
+        <v>-2.0139</v>
       </c>
       <c r="H15" t="n">
-        <v>6.7079</v>
+        <v>-1.6493</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4443</v>
+        <v>-0.3646</v>
       </c>
       <c r="J15" t="n">
-        <v>5.405</v>
+        <v>-0.5108</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3646</v>
+        <v>-0.5513</v>
       </c>
       <c r="L15" t="n">
         <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7472</v>
+        <v>-1.503</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3433</v>
+        <v>-1.098</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4039</v>
+        <v>-0.4051</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5778</v>
+        <v>-0.099</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1446</v>
+        <v>-0.403</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4332</v>
+        <v>0.304</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1675</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3811</v>
+        <v>-4.093999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5009</v>
+        <v>-12.919</v>
       </c>
       <c r="F16" t="n">
-        <v>3.8802</v>
+        <v>8.825100000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7514</v>
+        <v>1.2551</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3779</v>
+        <v>-10.8827</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3735</v>
+        <v>12.1376</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2088</v>
+        <v>4.8965</v>
       </c>
       <c r="K16" t="n">
-        <v>2.374</v>
+        <v>-0.5040000000000009</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8348</v>
+        <v>5.400799999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5426</v>
+        <v>-3.6414</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0039</v>
+        <v>-10.3786</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5387</v>
+        <v>6.737</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>-5.860300000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-20.5111</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>14.6508</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2298</v>
+        <v>2.5589</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.055</v>
+        <v>1.638300000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8252</v>
+        <v>0.9203999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5545</v>
+        <v>-2.0474</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>1.057</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
-      </c>
+        <v>-3.1042</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8734</v>
+        <v>7.5895</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3947</v>
+        <v>2.8419</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2682</v>
+        <v>4.7476</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.426</v>
+        <v>7.1522</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7475000000000001</v>
+        <v>6.7079</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1735</v>
+        <v>0.4443</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4293</v>
+        <v>5.405</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1215</v>
+        <v>5.3646</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3077</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0033</v>
+        <v>1.7472</v>
       </c>
       <c r="N17" t="n">
-        <v>0.869</v>
+        <v>1.3433</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1342</v>
+        <v>0.4039</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
         <v>2.7348</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2641</v>
+        <v>0.5778</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5432</v>
+        <v>0.1446</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8074</v>
+        <v>0.4332</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5545</v>
+        <v>0.2224</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-0.1675</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8611</v>
+        <v>3.7741</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2552</v>
+        <v>-0.1061</v>
       </c>
       <c r="F18" t="n">
-        <v>5.1163</v>
+        <v>3.8802</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7042</v>
+        <v>5.1444</v>
       </c>
       <c r="H18" t="n">
-        <v>3.975</v>
+        <v>3.3779</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.6792</v>
+        <v>1.7665</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5674</v>
+        <v>3.6018</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1108</v>
+        <v>2.374</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.6782</v>
+        <v>1.2278</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8632</v>
+        <v>1.5426</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8642</v>
+        <v>1.0039</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.001</v>
+        <v>0.5387</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1488</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1255</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2476</v>
+        <v>-0.2298</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.711</v>
+        <v>-1.055</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4634</v>
+        <v>0.8252</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6642</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1038</v>
+        <v>1.8734</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6085</v>
+        <v>-2.3947</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5048</v>
+        <v>4.2682</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7181</v>
+        <v>-0.426</v>
       </c>
       <c r="H19" t="n">
-        <v>0.089</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8071</v>
+        <v>-1.1735</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3892</v>
+        <v>-1.4293</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.1215</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-1.3077</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1073</v>
+        <v>1.0033</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8933</v>
+        <v>0.869</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.214</v>
+        <v>0.1342</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>2.7348</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1781</v>
+        <v>0.2641</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0007</v>
+        <v>-0.5432</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1789</v>
+        <v>0.8074</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6005</v>
+        <v>1.8611</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3599</v>
+        <v>-3.2552</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9605</v>
+        <v>5.1163</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.838</v>
+        <v>-0.7042</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1985</v>
+        <v>3.975</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0365</v>
+        <v>-4.6792</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8185</v>
+        <v>-1.5674</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3712</v>
+        <v>3.1108</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5527</v>
+        <v>-4.6782</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6565</v>
+        <v>0.8632</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1727</v>
+        <v>0.8642</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4838</v>
+        <v>-0.001</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>3.1255</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2118</v>
+        <v>-0.2476</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2642</v>
+        <v>-0.711</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.476</v>
+        <v>0.4634</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CAAMAÑO ALSINA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1861</v>
+        <v>1.521</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3676</v>
+        <v>1.521</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1815</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5326</v>
+        <v>1.521</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8583</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6743</v>
+        <v>1.214</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3277</v>
+        <v>1.521</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6536</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>1.214</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2049</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0963</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0399</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1362</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7797</v>
+        <v>0.607</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.201</v>
+        <v>0.607</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4212</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6759</v>
+        <v>0.607</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1236</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5523</v>
+        <v>0.607</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.516</v>
+        <v>0.607</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3689</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1471</v>
+        <v>0.607</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1599</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2454</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4052</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2918</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4858</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7829</v>
+        <v>0.1038</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1431</v>
+        <v>1.6085</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6398</v>
+        <v>-1.5048</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8813</v>
+        <v>-1.7181</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2497</v>
+        <v>0.089</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6317</v>
+        <v>-1.8071</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1548</v>
+        <v>0.3892</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.142</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0128</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7265</v>
+        <v>-2.1073</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1077</v>
+        <v>-0.8933</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6188</v>
+        <v>-1.214</v>
       </c>
       <c r="P23" t="n">
         <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2923</v>
+        <v>-0.1781</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3791</v>
+        <v>0.0007</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6714</v>
+        <v>-0.1789</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8724</v>
+        <v>-0.6005</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7827</v>
+        <v>1.3599</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0897</v>
+        <v>-1.9605</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3182</v>
+        <v>-1.838</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2351</v>
+        <v>0.1985</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5533</v>
+        <v>-2.0365</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7344</v>
+        <v>0.8185</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0731</v>
+        <v>1.3712</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6613</v>
+        <v>-0.5527</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0526</v>
+        <v>-2.6565</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.838</v>
+        <v>-1.1727</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2146</v>
+        <v>-1.4838</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0867</v>
+        <v>-0.2118</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4679</v>
+        <v>0.2642</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3812</v>
+        <v>-0.476</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0549</v>
+        <v>0.2772</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. CAAMANO ALSINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8425</v>
+        <v>-1.1861</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9922</v>
+        <v>-1.3676</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1497</v>
+        <v>0.1815</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.0643</v>
+        <v>-1.5326</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2167</v>
+        <v>-0.8583</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8476</v>
+        <v>-0.6743</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9192</v>
+        <v>-1.3277</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6536</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3077</v>
+        <v>-0.6741</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1451</v>
+        <v>-0.2049</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3948</v>
+        <v>-0.2047</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5399</v>
+        <v>-0.0002</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.0963</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1196</v>
+        <v>-0.0399</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4596</v>
+        <v>0.1362</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3869</v>
+        <v>0.0549</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3869</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.744800000000001</v>
+        <v>-1.7797</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.8253</v>
+        <v>-3.201</v>
       </c>
       <c r="F26" t="n">
+        <v>1.4212</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.6759</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.1236</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.5523</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.516</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-2.3689</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.1471</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.1599</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4052</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.4858</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J. GALVE NAVARRO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.7829</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.1431</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.6398</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.8813</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.2497</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.6317</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.1548</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.142</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-2.7265</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.1077</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.6188</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2923</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.6714</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S. IBORRA BARRERA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.8425</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-3.9922</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.1497</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.0643</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.2167</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.8476</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.9192</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.6114000000000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.1451</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.5790999999999999</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.1196</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.4596</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A. ABELLO GIRVES</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-3.3934</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-2.3037</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.0897</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-1.8392</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.07190000000000001</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1.7673</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.7661</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-2.0526</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-0.838</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-0.3812</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>play_by_play_2484371_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5.7448</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-8.825299999999999</v>
+      </c>
+      <c r="F30" t="n">
         <v>14.5699</v>
       </c>
-      <c r="G26" t="n">
-        <v>-1.254999999999999</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G30" t="n">
+        <v>-1.255000000000002</v>
+      </c>
+      <c r="H30" t="n">
         <v>10.8826</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I30" t="n">
         <v>-12.1377</v>
       </c>
-      <c r="J26" t="n">
-        <v>3.641500000000002</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J30" t="n">
+        <v>3.641500000000001</v>
+      </c>
+      <c r="K30" t="n">
         <v>10.3787</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L30" t="n">
         <v>-6.7369</v>
       </c>
-      <c r="M26" t="n">
-        <v>-4.896500000000001</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.5042000000000004</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="M30" t="n">
+        <v>-4.8965</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.5042000000000005</v>
+      </c>
+      <c r="O30" t="n">
         <v>-5.400700000000001</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P30" t="n">
         <v>5.860499999999999</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q30" t="n">
         <v>-14.6505</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R30" t="n">
         <v>20.511</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S30" t="n">
         <v>-0.9077999999999999</v>
       </c>
-      <c r="T26" t="n">
-        <v>-0.9204000000000002</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.01249999999999973</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="T30" t="n">
+        <v>-0.9204000000000001</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.01249999999999996</v>
+      </c>
+      <c r="V30" t="n">
         <v>2.0473</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W30" t="n">
         <v>3.1043</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X30" t="n">
         <v>-1.0569</v>
       </c>
+      <c r="Y30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
